--- a/形容動詞.xlsx
+++ b/形容動詞.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="動作（どうさ）" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="253">
   <si>
     <t>進出</t>
   </si>
@@ -179,6 +179,12 @@
     <t>かんき</t>
   </si>
   <si>
+    <t>増加</t>
+  </si>
+  <si>
+    <t>ぞうか</t>
+  </si>
+  <si>
     <t>延期</t>
   </si>
   <si>
@@ -191,6 +197,12 @@
     <t>ちょうか</t>
   </si>
   <si>
+    <t>減少</t>
+  </si>
+  <si>
+    <t>げんしょう</t>
+  </si>
+  <si>
     <t>再生</t>
   </si>
   <si>
@@ -278,22 +290,10 @@
     <t>てんかん</t>
   </si>
   <si>
-    <t>増加</t>
-  </si>
-  <si>
-    <t>ぞうか</t>
-  </si>
-  <si>
     <t>変換</t>
   </si>
   <si>
     <t>へんかん</t>
-  </si>
-  <si>
-    <t>減少</t>
-  </si>
-  <si>
-    <t>げんしょう</t>
   </si>
   <si>
     <t>変化</t>
@@ -663,6 +663,12 @@
     <t>きよう</t>
   </si>
   <si>
+    <t>代用</t>
+  </si>
+  <si>
+    <t>だいよう</t>
+  </si>
+  <si>
     <t>単調</t>
   </si>
   <si>
@@ -675,6 +681,18 @@
     <t>ふかけつな</t>
   </si>
   <si>
+    <t>振動</t>
+  </si>
+  <si>
+    <t>しんどう</t>
+  </si>
+  <si>
+    <t>緩和</t>
+  </si>
+  <si>
+    <t>かんわ</t>
+  </si>
+  <si>
     <t>発達</t>
   </si>
   <si>
@@ -684,6 +702,18 @@
     <t>（发达）</t>
   </si>
   <si>
+    <t>消耗</t>
+  </si>
+  <si>
+    <t>しょうもう</t>
+  </si>
+  <si>
+    <t>爆発</t>
+  </si>
+  <si>
+    <t>ばくはつ</t>
+  </si>
+  <si>
     <t>活躍</t>
   </si>
   <si>
@@ -718,6 +748,18 @@
   </si>
   <si>
     <t>せんしん</t>
+  </si>
+  <si>
+    <t>旺盛</t>
+  </si>
+  <si>
+    <t>おうせい</t>
+  </si>
+  <si>
+    <t>更新</t>
+  </si>
+  <si>
+    <t>こうしん</t>
   </si>
   <si>
     <t>専用</t>
@@ -859,7 +901,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -896,13 +938,6 @@
       <color theme="1"/>
       <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1358,157 +1393,160 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1951,112 +1989,124 @@
       </c>
     </row>
     <row r="7" spans="1:14">
+      <c r="A7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="E7" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:14">
+      <c r="A8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="E8" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="E9" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="E10" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="E11" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="E12" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="E13" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="E14" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>9</v>
@@ -2068,31 +2118,31 @@
     <row r="15" spans="1:14">
       <c r="C15" s="4"/>
       <c r="E15" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="C16" s="3"/>
       <c r="E16" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="3:14">
@@ -2141,7 +2191,7 @@
       </c>
     </row>
     <row r="21" spans="3:14">
-      <c r="C21" s="5"/>
+      <c r="C21" s="6"/>
       <c r="M21" s="1" t="s">
         <v>84</v>
       </c>
@@ -2161,7 +2211,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:K25"/>
+  <dimension ref="A2:K27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="16384" width="8.88888888888889" style="1"/>
@@ -2459,10 +2509,10 @@
         <v>172</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>173</v>
@@ -2481,49 +2531,79 @@
       <c r="C16" s="3" t="s">
         <v>172</v>
       </c>
+      <c r="E16" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>178</v>
+      </c>
       <c r="I16" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>182</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>188</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
         <v>163</v>
       </c>
@@ -2531,36 +2611,52 @@
         <v>164</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:10">
       <c r="A22" s="1" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="1" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="1" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="1" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>195</v>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -2577,174 +2673,174 @@
   <sheetData>
     <row r="2" ht="18" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="D3" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>

--- a/形容動詞.xlsx
+++ b/形容動詞.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="258">
   <si>
     <t>進出</t>
   </si>
@@ -720,10 +720,25 @@
     <t>かつやく</t>
   </si>
   <si>
+    <t>強引</t>
+  </si>
+  <si>
+    <t>ごういん</t>
+  </si>
+  <si>
     <t>自由</t>
   </si>
   <si>
     <t>じゆう</t>
+  </si>
+  <si>
+    <t>不確か</t>
+  </si>
+  <si>
+    <t>ふたしか</t>
+  </si>
+  <si>
+    <t>（不确定）</t>
   </si>
   <si>
     <t>正確</t>
@@ -2544,7 +2559,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
         <v>181</v>
       </c>
@@ -2564,7 +2579,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
         <v>187</v>
       </c>
@@ -2587,23 +2602,38 @@
         <v>193</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
         <v>194</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="I19" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>199</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
         <v>163</v>
       </c>
@@ -2611,52 +2641,52 @@
         <v>164</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="1" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="5" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -2673,174 +2703,174 @@
   <sheetData>
     <row r="2" ht="18" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/形容動詞.xlsx
+++ b/形容動詞.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="動作（どうさ）" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="264">
   <si>
     <t>進出</t>
   </si>
@@ -125,24 +125,30 @@
     <t>ゆうはつ</t>
   </si>
   <si>
+    <t>混合</t>
+  </si>
+  <si>
+    <t>こんごう</t>
+  </si>
+  <si>
+    <t>改善</t>
+  </si>
+  <si>
+    <t>かいぜん</t>
+  </si>
+  <si>
+    <t>統一</t>
+  </si>
+  <si>
+    <t>とういつ</t>
+  </si>
+  <si>
     <t>具有</t>
   </si>
   <si>
     <t>ぐゆう</t>
   </si>
   <si>
-    <t>改善</t>
-  </si>
-  <si>
-    <t>かいぜん</t>
-  </si>
-  <si>
-    <t>統一</t>
-  </si>
-  <si>
-    <t>とういつ</t>
-  </si>
-  <si>
     <t>進化</t>
   </si>
   <si>
@@ -155,22 +161,34 @@
     <t>てんかい</t>
   </si>
   <si>
+    <t>活用</t>
+  </si>
+  <si>
+    <t>かつよう</t>
+  </si>
+  <si>
+    <t>延長</t>
+  </si>
+  <si>
+    <t>えんちょう</t>
+  </si>
+  <si>
     <t>掲示</t>
   </si>
   <si>
     <t>けいじ</t>
   </si>
   <si>
-    <t>活用</t>
-  </si>
-  <si>
-    <t>かつよう</t>
-  </si>
-  <si>
-    <t>延長</t>
-  </si>
-  <si>
-    <t>えんちょう</t>
+    <t>増加</t>
+  </si>
+  <si>
+    <t>ぞうか</t>
+  </si>
+  <si>
+    <t>延期</t>
+  </si>
+  <si>
+    <t>えんき</t>
   </si>
   <si>
     <t>喚起</t>
@@ -179,16 +197,16 @@
     <t>かんき</t>
   </si>
   <si>
-    <t>増加</t>
-  </si>
-  <si>
-    <t>ぞうか</t>
-  </si>
-  <si>
-    <t>延期</t>
-  </si>
-  <si>
-    <t>えんき</t>
+    <t>減少</t>
+  </si>
+  <si>
+    <t>げんしょう</t>
+  </si>
+  <si>
+    <t>再生</t>
+  </si>
+  <si>
+    <t>さいせい</t>
   </si>
   <si>
     <t>超過</t>
@@ -197,16 +215,10 @@
     <t>ちょうか</t>
   </si>
   <si>
-    <t>減少</t>
-  </si>
-  <si>
-    <t>げんしょう</t>
-  </si>
-  <si>
-    <t>再生</t>
-  </si>
-  <si>
-    <t>さいせい</t>
+    <t>実現</t>
+  </si>
+  <si>
+    <t>じつげん</t>
   </si>
   <si>
     <t>接近</t>
@@ -215,10 +227,10 @@
     <t>せっきん</t>
   </si>
   <si>
-    <t>実現</t>
-  </si>
-  <si>
-    <t>じつげん</t>
+    <t>流行</t>
+  </si>
+  <si>
+    <t>りゅうこう</t>
   </si>
   <si>
     <t>成長</t>
@@ -227,10 +239,10 @@
     <t>せいちょう</t>
   </si>
   <si>
-    <t>流行</t>
-  </si>
-  <si>
-    <t>りゅうこう</t>
+    <t>拡散</t>
+  </si>
+  <si>
+    <t>かくさん</t>
   </si>
   <si>
     <t>普及</t>
@@ -239,10 +251,13 @@
     <t>ふきゅう</t>
   </si>
   <si>
-    <t>拡散</t>
-  </si>
-  <si>
-    <t>かくさん</t>
+    <t>生成</t>
+  </si>
+  <si>
+    <t>せいせい</t>
+  </si>
+  <si>
+    <t>生成物｜せいせいぶつ</t>
   </si>
   <si>
     <t>突破</t>
@@ -251,13 +266,10 @@
     <t>とっぱ</t>
   </si>
   <si>
-    <t>生成</t>
-  </si>
-  <si>
-    <t>せいせい</t>
-  </si>
-  <si>
-    <t>生成物｜せいせいぶつ</t>
+    <t>縮小</t>
+  </si>
+  <si>
+    <t>しゅくしょう</t>
   </si>
   <si>
     <t>一致</t>
@@ -266,10 +278,10 @@
     <t>いっち</t>
   </si>
   <si>
-    <t>縮小</t>
-  </si>
-  <si>
-    <t>しゅくしょう</t>
+    <t>拡大</t>
+  </si>
+  <si>
+    <t>かくだい</t>
   </si>
   <si>
     <t>表示</t>
@@ -278,12 +290,6 @@
     <t>ひょうじ</t>
   </si>
   <si>
-    <t>拡大</t>
-  </si>
-  <si>
-    <t>かくだい</t>
-  </si>
-  <si>
     <t>転換</t>
   </si>
   <si>
@@ -302,16 +308,16 @@
     <t>へんか</t>
   </si>
   <si>
+    <t>稼働</t>
+  </si>
+  <si>
+    <t>かどう</t>
+  </si>
+  <si>
     <t>抑制</t>
   </si>
   <si>
     <t>よくせい</t>
-  </si>
-  <si>
-    <t>稼働</t>
-  </si>
-  <si>
-    <t>かどう</t>
   </si>
   <si>
     <t>促進</t>
@@ -720,6 +726,12 @@
     <t>かつやく</t>
   </si>
   <si>
+    <t>圧縮</t>
+  </si>
+  <si>
+    <t>あっしゅく</t>
+  </si>
+  <si>
     <t>強引</t>
   </si>
   <si>
@@ -904,6 +916,12 @@
   </si>
   <si>
     <t>意外</t>
+  </si>
+  <si>
+    <t>甚大</t>
+  </si>
+  <si>
+    <t>じんだい</t>
   </si>
 </sst>
 </file>
@@ -1957,30 +1975,30 @@
         <v>20</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -2124,55 +2142,55 @@
         <v>67</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="C15" s="4"/>
       <c r="E15" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="C16" s="3"/>
       <c r="E16" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="3:14">
       <c r="C17" s="3"/>
       <c r="E17" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="3:14">
@@ -2212,6 +2230,14 @@
       </c>
       <c r="N21" s="1" t="s">
         <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14">
+      <c r="M22" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="3:14">
@@ -2234,459 +2260,471 @@
   <sheetData>
     <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="5" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -2698,179 +2736,187 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:E21"/>
+  <dimension ref="A2:E22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
   <sheetData>
     <row r="2" ht="18" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>262</v>
+      </c>
+      <c r="B22" t="s">
+        <v>263</v>
       </c>
     </row>
   </sheetData>

--- a/形容動詞.xlsx
+++ b/形容動詞.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="270">
   <si>
     <t>進出</t>
   </si>
@@ -320,6 +320,12 @@
     <t>よくせい</t>
   </si>
   <si>
+    <t>拡充</t>
+  </si>
+  <si>
+    <t>かくじゅう</t>
+  </si>
+  <si>
     <t>促進</t>
   </si>
   <si>
@@ -753,6 +759,12 @@
     <t>（不确定）</t>
   </si>
   <si>
+    <t>希薄</t>
+  </si>
+  <si>
+    <t>きはく</t>
+  </si>
+  <si>
     <t>正確</t>
   </si>
   <si>
@@ -787,6 +799,12 @@
   </si>
   <si>
     <t>こうしん</t>
+  </si>
+  <si>
+    <t>好況</t>
+  </si>
+  <si>
+    <t>こうきょう</t>
   </si>
   <si>
     <t>専用</t>
@@ -2208,36 +2226,42 @@
       </c>
     </row>
     <row r="19" spans="3:14">
+      <c r="E19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="M19" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="3:14">
       <c r="M20" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="3:14">
       <c r="C21" s="6"/>
       <c r="M21" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="3:14">
       <c r="M22" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="3:14">
@@ -2252,7 +2276,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:K27"/>
+  <dimension ref="A2:K28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="16384" width="8.88888888888889" style="1"/>
@@ -2260,294 +2284,294 @@
   <sheetData>
     <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>64</v>
@@ -2556,104 +2580,104 @@
         <v>65</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>19</v>
@@ -2662,69 +2686,83 @@
         <v>20</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -2741,182 +2779,182 @@
   <sheetData>
     <row r="2" ht="18" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B22" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>
